--- a/SGC-CKN/Excel/6cca0229-d127-46a2-b028-dadc8630daf4_Lô_đất_ký_hiệu_CT-02_P7-163_D800_12-03-2026.xlsx
+++ b/SGC-CKN/Excel/6cca0229-d127-46a2-b028-dadc8630daf4_Lô_đất_ký_hiệu_CT-02_P7-163_D800_12-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="74">
   <si>
     <t>Dự án</t>
   </si>
@@ -195,7 +195,7 @@
     <t>TK-16.1.Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">17:55
+    <t xml:space="preserve">17:59
 12/03/2026</t>
   </si>
   <si>
@@ -209,7 +209,7 @@
 12/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">19:20
+    <t xml:space="preserve">18:19
 12/03/2026</t>
   </si>
   <si>
@@ -219,11 +219,7 @@
     <t>Cuội đa màu sắc TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">19:25
-12/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:45
+    <t xml:space="preserve">20:06
 12/03/2026</t>
   </si>
   <si>
@@ -1245,7 +1241,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-7.4</v>
@@ -1254,10 +1250,10 @@
         <v>0.73</v>
       </c>
       <c r="I11" s="5">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="J11" s="8">
-        <v>8.86</v>
+        <v>10.09</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1496,13 +1492,13 @@
         <v>-42.4</v>
       </c>
       <c r="H18" s="28">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="I18" s="28">
         <v>1</v>
       </c>
       <c r="J18" s="31">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1531,13 +1527,13 @@
         <v>-44.4</v>
       </c>
       <c r="H19" s="32">
-        <v>1.33</v>
+        <v>0.32</v>
       </c>
       <c r="I19" s="32">
         <v>2</v>
       </c>
-      <c r="J19" s="12">
-        <v>1.5</v>
+      <c r="J19" s="8">
+        <v>6.32</v>
       </c>
       <c r="K19" s="33" t="s">
         <v>30</v>
@@ -1554,10 +1550,10 @@
         <v>62</v>
       </c>
       <c r="D20" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="37" t="s">
         <v>63</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>64</v>
       </c>
       <c r="F20" s="35">
         <v>-44.4</v>
@@ -1566,13 +1562,13 @@
         <v>-45.13</v>
       </c>
       <c r="H20" s="35">
-        <v>0.33</v>
+        <v>1.78</v>
       </c>
       <c r="I20" s="35">
         <v>0.73</v>
       </c>
-      <c r="J20" s="12">
-        <v>2.19</v>
+      <c r="J20" s="31">
+        <v>0.41</v>
       </c>
       <c r="K20" s="36" t="s">
         <v>30</v>
@@ -1580,7 +1576,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B23" s="38"/>
       <c r="C23" s="38"/>
@@ -1686,31 +1682,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1727,7 +1723,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-7.4</v>
@@ -1736,10 +1732,10 @@
         <v>0.73</v>
       </c>
       <c r="H2" s="5">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="I2" s="8">
-        <v>8.86</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1936,13 +1932,13 @@
         <v>-42.4</v>
       </c>
       <c r="G9" s="28">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="H9" s="28">
         <v>1</v>
       </c>
       <c r="I9" s="31">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1965,13 +1961,13 @@
         <v>-44.4</v>
       </c>
       <c r="G10" s="32">
-        <v>1.33</v>
+        <v>0.32</v>
       </c>
       <c r="H10" s="32">
         <v>2</v>
       </c>
-      <c r="I10" s="12">
-        <v>1.5</v>
+      <c r="I10" s="8">
+        <v>6.32</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1994,18 +1990,18 @@
         <v>-45.13</v>
       </c>
       <c r="G11" s="35">
-        <v>0.33</v>
+        <v>1.78</v>
       </c>
       <c r="H11" s="35">
         <v>0.73</v>
       </c>
-      <c r="I11" s="12">
-        <v>2.19</v>
+      <c r="I11" s="31">
+        <v>0.41</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B12" s="40" t="s">
         <v>30</v>
@@ -2017,19 +2013,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="40">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="F12" s="40">
         <v>-45.13</v>
       </c>
       <c r="G12" s="40">
-        <v>11.42</v>
+        <v>11.92</v>
       </c>
       <c r="H12" s="40">
-        <v>44.23</v>
+        <v>45.13</v>
       </c>
       <c r="I12" s="40">
-        <v>3.87</v>
+        <v>3.79</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/6cca0229-d127-46a2-b028-dadc8630daf4_Lô_đất_ký_hiệu_CT-02_P7-163_D800_12-03-2026.xlsx
+++ b/SGC-CKN/Excel/6cca0229-d127-46a2-b028-dadc8630daf4_Lô_đất_ký_hiệu_CT-02_P7-163_D800_12-03-2026.xlsx
@@ -219,7 +219,7 @@
     <t>Cuội đa màu sắc TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">20:06
+    <t xml:space="preserve">20:05
 12/03/2026</t>
   </si>
   <si>
@@ -1562,7 +1562,7 @@
         <v>-45.13</v>
       </c>
       <c r="H20" s="35">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="I20" s="35">
         <v>0.73</v>
@@ -1990,7 +1990,7 @@
         <v>-45.13</v>
       </c>
       <c r="G11" s="35">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H11" s="35">
         <v>0.73</v>
@@ -2019,7 +2019,7 @@
         <v>-45.13</v>
       </c>
       <c r="G12" s="40">
-        <v>11.92</v>
+        <v>11.9</v>
       </c>
       <c r="H12" s="40">
         <v>45.13</v>
